--- a/html/Kiropraktorsystemer_excel.XLSX
+++ b/html/Kiropraktorsystemer_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD66A840-5401-4EB7-AA43-E986C2786860}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7EC9E0A-EE88-4D1D-A7B3-CF19B961A9ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30855" yWindow="1950" windowWidth="21600" windowHeight="11235" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 19-12-2025" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 29-01-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Kiropraktorsystemer">'Opdateret d. 19-12-2025'!$A$1:$J$32</definedName>
+    <definedName name="Kiropraktorsystemer">'Opdateret d. 29-01-2026'!$A$1:$J$32</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Kiropraktorsystemer_excel.XLSX
+++ b/html/Kiropraktorsystemer_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7EC9E0A-EE88-4D1D-A7B3-CF19B961A9ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AD19C66-3070-43D2-A831-BFB02D978E58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 29-01-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 02-02-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Kiropraktorsystemer">'Opdateret d. 29-01-2026'!$A$1:$J$32</definedName>
+    <definedName name="Kiropraktorsystemer">'Opdateret d. 02-02-2026'!$A$1:$J$32</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Kiropraktorsystemer_excel.XLSX
+++ b/html/Kiropraktorsystemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AD19C66-3070-43D2-A831-BFB02D978E58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D158A67-01BC-444B-B130-1472DC49D9F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 02-02-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 20-02-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Kiropraktorsystemer">'Opdateret d. 02-02-2026'!$A$1:$J$32</definedName>
+    <definedName name="Kiropraktorsystemer">'Opdateret d. 20-02-2026'!$A$1:$J$32</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -524,9 +524,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J32"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -558,7 +558,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -590,7 +590,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>14</v>
       </c>
@@ -622,7 +622,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>16</v>
       </c>
@@ -654,7 +654,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>19</v>
       </c>
@@ -680,7 +680,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>21</v>
       </c>
@@ -712,7 +712,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>24</v>
       </c>
@@ -741,7 +741,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>26</v>
       </c>
@@ -764,7 +764,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>26</v>
       </c>
@@ -793,7 +793,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>29</v>
       </c>
@@ -822,7 +822,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>29</v>
       </c>
@@ -851,7 +851,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>32</v>
       </c>
@@ -880,7 +880,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>32</v>
       </c>
@@ -912,7 +912,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>35</v>
       </c>
@@ -941,7 +941,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>37</v>
       </c>
@@ -964,7 +964,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>37</v>
       </c>
@@ -987,7 +987,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>40</v>
       </c>
@@ -1001,7 +1001,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>42</v>
       </c>
@@ -1015,7 +1015,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>44</v>
       </c>
@@ -1047,7 +1047,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>10</v>
       </c>
@@ -1079,7 +1079,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>14</v>
       </c>
@@ -1111,7 +1111,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>16</v>
       </c>
@@ -1143,7 +1143,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>47</v>
       </c>
@@ -1175,7 +1175,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>24</v>
       </c>
@@ -1204,7 +1204,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>29</v>
       </c>
@@ -1236,7 +1236,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>29</v>
       </c>
@@ -1268,7 +1268,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>32</v>
       </c>
@@ -1297,7 +1297,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>32</v>
       </c>
@@ -1314,7 +1314,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>40</v>
       </c>
@@ -1328,7 +1328,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>49</v>
       </c>
@@ -1342,7 +1342,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>42</v>
       </c>
@@ -1356,7 +1356,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>51</v>
       </c>

--- a/html/Kiropraktorsystemer_excel.XLSX
+++ b/html/Kiropraktorsystemer_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D158A67-01BC-444B-B130-1472DC49D9F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A336197-2BD8-4AD1-ACA7-1774F27523D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 20-02-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 04-03-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Kiropraktorsystemer">'Opdateret d. 20-02-2026'!$A$1:$J$32</definedName>
+    <definedName name="Kiropraktorsystemer">'Opdateret d. 04-03-2026'!$A$1:$J$32</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Kiropraktorsystemer_excel.XLSX
+++ b/html/Kiropraktorsystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A336197-2BD8-4AD1-ACA7-1774F27523D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93BD5DAD-0EEF-477F-8F03-1BB5ED1487B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 04-03-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 06-03-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Kiropraktorsystemer">'Opdateret d. 04-03-2026'!$A$1:$J$32</definedName>
+    <definedName name="Kiropraktorsystemer">'Opdateret d. 06-03-2026'!$A$1:$J$32</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Kiropraktorsystemer_excel.XLSX
+++ b/html/Kiropraktorsystemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93BD5DAD-0EEF-477F-8F03-1BB5ED1487B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B83CAB1D-DC8A-4BAF-9127-E778B400D13C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Kiropraktorsystemer_excel.XLSX
+++ b/html/Kiropraktorsystemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B83CAB1D-DC8A-4BAF-9127-E778B400D13C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42F75B9C-5115-47F7-842D-3D622AB75C31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Kiropraktorsystemer_excel.XLSX
+++ b/html/Kiropraktorsystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42F75B9C-5115-47F7-842D-3D622AB75C31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4E8ABDB-EB58-43FD-8181-85F194B16BB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14625" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 06-03-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 09-03-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Kiropraktorsystemer">'Opdateret d. 06-03-2026'!$A$1:$J$32</definedName>
+    <definedName name="Kiropraktorsystemer">'Opdateret d. 09-03-2026'!$A$1:$J$32</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Kiropraktorsystemer_excel.XLSX
+++ b/html/Kiropraktorsystemer_excel.XLSX
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4E8ABDB-EB58-43FD-8181-85F194B16BB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8164E0D8-A196-4658-91C7-3061A7A51883}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14625" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 09-03-2026" sheetId="1" r:id="rId1"/>

--- a/html/Kiropraktorsystemer_excel.XLSX
+++ b/html/Kiropraktorsystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8164E0D8-A196-4658-91C7-3061A7A51883}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F4177EF-68E2-4D72-BF3D-5F3E30E803FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 09-03-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 11-03-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Kiropraktorsystemer">'Opdateret d. 09-03-2026'!$A$1:$J$32</definedName>
+    <definedName name="Kiropraktorsystemer">'Opdateret d. 11-03-2026'!$A$1:$J$32</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Kiropraktorsystemer_excel.XLSX
+++ b/html/Kiropraktorsystemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F4177EF-68E2-4D72-BF3D-5F3E30E803FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EB44DD0-1A46-43FF-9A76-FE3F9FC4D551}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Kiropraktorsystemer_excel.XLSX
+++ b/html/Kiropraktorsystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EB44DD0-1A46-43FF-9A76-FE3F9FC4D551}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7841261-6F59-41B7-BF50-1FE96E5B937C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 11-03-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 20-03-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Kiropraktorsystemer">'Opdateret d. 11-03-2026'!$A$1:$J$32</definedName>
+    <definedName name="Kiropraktorsystemer">'Opdateret d. 20-03-2026'!$A$1:$J$32</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Kiropraktorsystemer_excel.XLSX
+++ b/html/Kiropraktorsystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7841261-6F59-41B7-BF50-1FE96E5B937C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7A4B223-D6A7-45F1-8982-F5D10161712F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 20-03-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 25-03-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Kiropraktorsystemer">'Opdateret d. 20-03-2026'!$A$1:$J$32</definedName>
+    <definedName name="Kiropraktorsystemer">'Opdateret d. 25-03-2026'!$A$1:$J$32</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Kiropraktorsystemer_excel.XLSX
+++ b/html/Kiropraktorsystemer_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7A4B223-D6A7-45F1-8982-F5D10161712F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9B6411C-2496-441E-AA2D-E55F9B5BCFA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 25-03-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 08-04-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Kiropraktorsystemer">'Opdateret d. 25-03-2026'!$A$1:$J$32</definedName>
+    <definedName name="Kiropraktorsystemer">'Opdateret d. 08-04-2026'!$A$1:$J$32</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Kiropraktorsystemer_excel.XLSX
+++ b/html/Kiropraktorsystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9B6411C-2496-441E-AA2D-E55F9B5BCFA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{727292AD-0DDB-4EBF-BA63-6356FDE6DB30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 08-04-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 10-04-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Kiropraktorsystemer">'Opdateret d. 08-04-2026'!$A$1:$J$32</definedName>
+    <definedName name="Kiropraktorsystemer">'Opdateret d. 10-04-2026'!$A$1:$J$32</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Kiropraktorsystemer_excel.XLSX
+++ b/html/Kiropraktorsystemer_excel.XLSX
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{727292AD-0DDB-4EBF-BA63-6356FDE6DB30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E46A9DD-8573-4BAA-83AD-C53C90E51525}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-15045" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 10-04-2026" sheetId="1" r:id="rId1"/>

--- a/html/Kiropraktorsystemer_excel.XLSX
+++ b/html/Kiropraktorsystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E46A9DD-8573-4BAA-83AD-C53C90E51525}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17D7BBA3-5683-4E25-8C20-BE8FD5A9E282}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-15045" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 10-04-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 14-04-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Kiropraktorsystemer">'Opdateret d. 10-04-2026'!$A$1:$J$32</definedName>
+    <definedName name="Kiropraktorsystemer">'Opdateret d. 14-04-2026'!$A$1:$J$32</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Kiropraktorsystemer_excel.XLSX
+++ b/html/Kiropraktorsystemer_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17D7BBA3-5683-4E25-8C20-BE8FD5A9E282}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A213557C-0CEA-41EB-914D-FD5EDD115BE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 14-04-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 24-04-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Kiropraktorsystemer">'Opdateret d. 14-04-2026'!$A$1:$J$32</definedName>
+    <definedName name="Kiropraktorsystemer">'Opdateret d. 24-04-2026'!$A$1:$J$32</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Kiropraktorsystemer_excel.XLSX
+++ b/html/Kiropraktorsystemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A213557C-0CEA-41EB-914D-FD5EDD115BE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F850E23-6880-46BA-9437-C6A0F5D238EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Kiropraktorsystemer_excel.XLSX
+++ b/html/Kiropraktorsystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F850E23-6880-46BA-9437-C6A0F5D238EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10E490AF-531F-47DD-806D-D0D466C9C2B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 24-04-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 27-04-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Kiropraktorsystemer">'Opdateret d. 24-04-2026'!$A$1:$J$32</definedName>
+    <definedName name="Kiropraktorsystemer">'Opdateret d. 27-04-2026'!$A$1:$J$32</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Kiropraktorsystemer_excel.XLSX
+++ b/html/Kiropraktorsystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10E490AF-531F-47DD-806D-D0D466C9C2B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FAED318-C1F2-4556-87D5-C874B787B1AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="384" yWindow="384" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 27-04-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 06-05-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Kiropraktorsystemer">'Opdateret d. 27-04-2026'!$A$1:$J$32</definedName>
+    <definedName name="Kiropraktorsystemer">'Opdateret d. 06-05-2026'!$A$1:$J$32</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Kiropraktorsystemer_excel.XLSX
+++ b/html/Kiropraktorsystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FAED318-C1F2-4556-87D5-C874B787B1AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A69EC683-6D06-49BB-878B-EC31F97C3540}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="384" yWindow="384" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 06-05-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 01-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Kiropraktorsystemer">'Opdateret d. 06-05-2026'!$A$1:$J$32</definedName>
+    <definedName name="Kiropraktorsystemer">'Opdateret d. 01-06-2026'!$A$1:$J$32</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Kiropraktorsystemer_excel.XLSX
+++ b/html/Kiropraktorsystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A69EC683-6D06-49BB-878B-EC31F97C3540}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A806F4F-0144-45DF-97C0-B0C13090F4F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 01-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 02-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Kiropraktorsystemer">'Opdateret d. 01-06-2026'!$A$1:$J$32</definedName>
+    <definedName name="Kiropraktorsystemer">'Opdateret d. 02-06-2026'!$A$1:$J$32</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Kiropraktorsystemer_excel.XLSX
+++ b/html/Kiropraktorsystemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A806F4F-0144-45DF-97C0-B0C13090F4F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3756489B-21CA-4CD2-A9F2-AF3219A3F6B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Kiropraktorsystemer_excel.XLSX
+++ b/html/Kiropraktorsystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3756489B-21CA-4CD2-A9F2-AF3219A3F6B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5059061E-E6E3-4DDC-9CFF-002D2905DDFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 02-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 05-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Kiropraktorsystemer">'Opdateret d. 02-06-2026'!$A$1:$J$32</definedName>
+    <definedName name="Kiropraktorsystemer">'Opdateret d. 05-06-2026'!$A$1:$J$32</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Kiropraktorsystemer_excel.XLSX
+++ b/html/Kiropraktorsystemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7EC9E0A-EE88-4D1D-A7B3-CF19B961A9ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48DD5711-06F0-4A44-BE33-60A055893A4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Kiropraktorsystemer_excel.XLSX
+++ b/html/Kiropraktorsystemer_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48DD5711-06F0-4A44-BE33-60A055893A4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EBE613D-4FDC-4557-8187-D4704AA12B8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3150" yWindow="3135" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 29-01-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 09-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Kiropraktorsystemer">'Opdateret d. 29-01-2026'!$A$1:$J$32</definedName>
+    <definedName name="Kiropraktorsystemer">'Opdateret d. 09-06-2026'!$A$1:$J$32</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Kiropraktorsystemer_excel.XLSX
+++ b/html/Kiropraktorsystemer_excel.XLSX
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EBE613D-4FDC-4557-8187-D4704AA12B8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8583A92-7B7F-49DF-80C1-43E87CD8C541}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3150" yWindow="3135" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 09-06-2026" sheetId="1" r:id="rId1"/>

--- a/html/Kiropraktorsystemer_excel.XLSX
+++ b/html/Kiropraktorsystemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8583A92-7B7F-49DF-80C1-43E87CD8C541}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60BB934F-A20B-4116-A4A8-2830D2931122}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Kiropraktorsystemer_excel.XLSX
+++ b/html/Kiropraktorsystemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60BB934F-A20B-4116-A4A8-2830D2931122}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D397D31-241C-41AF-BCB0-68CE22344389}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 09-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 15-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Kiropraktorsystemer">'Opdateret d. 09-06-2026'!$A$1:$J$32</definedName>
+    <definedName name="Kiropraktorsystemer">'Opdateret d. 15-06-2026'!$A$1:$J$32</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -524,9 +524,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J32"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -558,7 +558,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -590,7 +590,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>14</v>
       </c>
@@ -622,7 +622,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>16</v>
       </c>
@@ -654,7 +654,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>19</v>
       </c>
@@ -680,7 +680,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>21</v>
       </c>
@@ -712,7 +712,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>24</v>
       </c>
@@ -741,7 +741,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>26</v>
       </c>
@@ -764,7 +764,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>26</v>
       </c>
@@ -793,7 +793,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>29</v>
       </c>
@@ -822,7 +822,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>29</v>
       </c>
@@ -851,7 +851,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>32</v>
       </c>
@@ -880,7 +880,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>32</v>
       </c>
@@ -912,7 +912,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>35</v>
       </c>
@@ -941,7 +941,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>37</v>
       </c>
@@ -964,7 +964,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>37</v>
       </c>
@@ -987,7 +987,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>40</v>
       </c>
@@ -1001,7 +1001,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>42</v>
       </c>
@@ -1015,7 +1015,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>44</v>
       </c>
@@ -1047,7 +1047,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>10</v>
       </c>
@@ -1079,7 +1079,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>14</v>
       </c>
@@ -1111,7 +1111,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>16</v>
       </c>
@@ -1143,7 +1143,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>47</v>
       </c>
@@ -1175,7 +1175,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>24</v>
       </c>
@@ -1204,7 +1204,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>29</v>
       </c>
@@ -1236,7 +1236,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>29</v>
       </c>
@@ -1268,7 +1268,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>32</v>
       </c>
@@ -1297,7 +1297,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>32</v>
       </c>
@@ -1314,7 +1314,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>40</v>
       </c>
@@ -1328,7 +1328,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>49</v>
       </c>
@@ -1342,7 +1342,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>42</v>
       </c>
@@ -1356,7 +1356,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>51</v>
       </c>

--- a/html/Kiropraktorsystemer_excel.XLSX
+++ b/html/Kiropraktorsystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D397D31-241C-41AF-BCB0-68CE22344389}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBD6AC62-DE7E-4FE2-A0CF-A22775DCDDB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 15-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 22-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Kiropraktorsystemer">'Opdateret d. 15-06-2026'!$A$1:$J$32</definedName>
+    <definedName name="Kiropraktorsystemer">'Opdateret d. 22-06-2026'!$A$1:$J$32</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Kiropraktorsystemer_excel.XLSX
+++ b/html/Kiropraktorsystemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBD6AC62-DE7E-4FE2-A0CF-A22775DCDDB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4811351E-7568-422B-95CF-39E7FD81C8CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 22-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 23-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Kiropraktorsystemer">'Opdateret d. 22-06-2026'!$A$1:$J$32</definedName>
+    <definedName name="Kiropraktorsystemer">'Opdateret d. 23-06-2026'!$A$1:$J$32</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -524,9 +524,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J32"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -558,7 +558,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -590,7 +590,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>14</v>
       </c>
@@ -622,7 +622,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>16</v>
       </c>
@@ -654,7 +654,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>19</v>
       </c>
@@ -680,7 +680,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>21</v>
       </c>
@@ -712,7 +712,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>24</v>
       </c>
@@ -741,7 +741,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>26</v>
       </c>
@@ -764,7 +764,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>26</v>
       </c>
@@ -793,7 +793,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>29</v>
       </c>
@@ -822,7 +822,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>29</v>
       </c>
@@ -851,7 +851,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>32</v>
       </c>
@@ -880,7 +880,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>32</v>
       </c>
@@ -912,7 +912,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>35</v>
       </c>
@@ -941,7 +941,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>37</v>
       </c>
@@ -964,7 +964,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>37</v>
       </c>
@@ -987,7 +987,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>40</v>
       </c>
@@ -1001,7 +1001,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>42</v>
       </c>
@@ -1015,7 +1015,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>44</v>
       </c>
@@ -1047,7 +1047,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>10</v>
       </c>
@@ -1079,7 +1079,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>14</v>
       </c>
@@ -1111,7 +1111,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>16</v>
       </c>
@@ -1143,7 +1143,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>47</v>
       </c>
@@ -1175,7 +1175,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>24</v>
       </c>
@@ -1204,7 +1204,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>29</v>
       </c>
@@ -1236,7 +1236,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>29</v>
       </c>
@@ -1268,7 +1268,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>32</v>
       </c>
@@ -1297,7 +1297,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>32</v>
       </c>
@@ -1314,7 +1314,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>40</v>
       </c>
@@ -1328,7 +1328,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>49</v>
       </c>
@@ -1342,7 +1342,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>42</v>
       </c>
@@ -1356,7 +1356,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>51</v>
       </c>

--- a/html/Kiropraktorsystemer_excel.XLSX
+++ b/html/Kiropraktorsystemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4811351E-7568-422B-95CF-39E7FD81C8CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCD8901F-C7DB-40DE-BDC5-4BE3C0E42C14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Kiropraktorsystemer_excel.XLSX
+++ b/html/Kiropraktorsystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBD6AC62-DE7E-4FE2-A0CF-A22775DCDDB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0782073B-D33A-4C0A-92C0-175D0762196B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2304" yWindow="2304" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 22-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 23-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Kiropraktorsystemer">'Opdateret d. 22-06-2026'!$A$1:$J$32</definedName>
+    <definedName name="Kiropraktorsystemer">'Opdateret d. 23-06-2026'!$A$1:$J$32</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -52,7 +52,7 @@
     <t>FrontCare _Kiro_ (Frontspeed)</t>
   </si>
   <si>
-    <t>KirCacs (NIKKB)</t>
+    <t>KirCacs (Fonden for Kiropraktorernes Videnscenter)</t>
   </si>
   <si>
     <t>Negativ kvittering</t>

--- a/html/Kiropraktorsystemer_excel.XLSX
+++ b/html/Kiropraktorsystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0782073B-D33A-4C0A-92C0-175D0762196B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E705DB89-C9A9-4746-80E0-6BAC11AFE4DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2304" yWindow="2304" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 23-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 25-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Kiropraktorsystemer">'Opdateret d. 23-06-2026'!$A$1:$J$32</definedName>
+    <definedName name="Kiropraktorsystemer">'Opdateret d. 25-06-2026'!$A$1:$J$32</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Kiropraktorsystemer_excel.XLSX
+++ b/html/Kiropraktorsystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E705DB89-C9A9-4746-80E0-6BAC11AFE4DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94636A57-73A2-491C-B0C1-541F52B2BDD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2304" yWindow="2304" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 25-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 30-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Kiropraktorsystemer">'Opdateret d. 25-06-2026'!$A$1:$J$32</definedName>
+    <definedName name="Kiropraktorsystemer">'Opdateret d. 30-06-2026'!$A$1:$J$32</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Kiropraktorsystemer_excel.XLSX
+++ b/html/Kiropraktorsystemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94636A57-73A2-491C-B0C1-541F52B2BDD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17698FA9-F77B-4363-92C5-1570FA5CFD9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Kiropraktorsystemer_excel.XLSX
+++ b/html/Kiropraktorsystemer_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17698FA9-F77B-4363-92C5-1570FA5CFD9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BCCD339-8A08-4D2B-9900-78A858732DF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 30-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 01-07-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Kiropraktorsystemer">'Opdateret d. 30-06-2026'!$A$1:$J$32</definedName>
+    <definedName name="Kiropraktorsystemer">'Opdateret d. 01-07-2026'!$A$1:$J$32</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -524,9 +524,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J32"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -558,7 +558,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -590,7 +590,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>14</v>
       </c>
@@ -622,7 +622,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>16</v>
       </c>
@@ -654,7 +654,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>19</v>
       </c>
@@ -680,7 +680,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>21</v>
       </c>
@@ -712,7 +712,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>24</v>
       </c>
@@ -741,7 +741,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>26</v>
       </c>
@@ -764,7 +764,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>26</v>
       </c>
@@ -793,7 +793,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>29</v>
       </c>
@@ -822,7 +822,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>29</v>
       </c>
@@ -851,7 +851,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>32</v>
       </c>
@@ -880,7 +880,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>32</v>
       </c>
@@ -912,7 +912,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>35</v>
       </c>
@@ -941,7 +941,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>37</v>
       </c>
@@ -964,7 +964,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>37</v>
       </c>
@@ -987,7 +987,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>40</v>
       </c>
@@ -1001,7 +1001,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>42</v>
       </c>
@@ -1015,7 +1015,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>44</v>
       </c>
@@ -1047,7 +1047,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>10</v>
       </c>
@@ -1079,7 +1079,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>14</v>
       </c>
@@ -1111,7 +1111,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>16</v>
       </c>
@@ -1143,7 +1143,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>47</v>
       </c>
@@ -1175,7 +1175,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>24</v>
       </c>
@@ -1204,7 +1204,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>29</v>
       </c>
@@ -1236,7 +1236,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>29</v>
       </c>
@@ -1268,7 +1268,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>32</v>
       </c>
@@ -1297,7 +1297,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>32</v>
       </c>
@@ -1314,7 +1314,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>40</v>
       </c>
@@ -1328,7 +1328,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>49</v>
       </c>
@@ -1342,7 +1342,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>42</v>
       </c>
@@ -1356,7 +1356,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>51</v>
       </c>

--- a/html/Kiropraktorsystemer_excel.XLSX
+++ b/html/Kiropraktorsystemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BCCD339-8A08-4D2B-9900-78A858732DF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8E83F2A-6252-43FE-AF40-38BB1B942768}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 01-07-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 02-07-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Kiropraktorsystemer">'Opdateret d. 01-07-2026'!$A$1:$J$32</definedName>
+    <definedName name="Kiropraktorsystemer">'Opdateret d. 02-07-2026'!$A$1:$J$32</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Kiropraktorsystemer_excel.XLSX
+++ b/html/Kiropraktorsystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BCCD339-8A08-4D2B-9900-78A858732DF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65B6A2E8-A19B-48FE-9B9D-60DDAFE3CC7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 01-07-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 03-07-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Kiropraktorsystemer">'Opdateret d. 01-07-2026'!$A$1:$J$32</definedName>
+    <definedName name="Kiropraktorsystemer">'Opdateret d. 03-07-2026'!$A$1:$J$32</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -524,9 +524,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J32"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -558,7 +558,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -590,7 +590,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>14</v>
       </c>
@@ -622,7 +622,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>16</v>
       </c>
@@ -654,7 +654,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>19</v>
       </c>
@@ -680,7 +680,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>21</v>
       </c>
@@ -712,7 +712,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>24</v>
       </c>
@@ -741,7 +741,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>26</v>
       </c>
@@ -764,7 +764,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>26</v>
       </c>
@@ -793,7 +793,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>29</v>
       </c>
@@ -822,7 +822,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>29</v>
       </c>
@@ -851,7 +851,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>32</v>
       </c>
@@ -880,7 +880,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>32</v>
       </c>
@@ -912,7 +912,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>35</v>
       </c>
@@ -941,7 +941,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>37</v>
       </c>
@@ -964,7 +964,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>37</v>
       </c>
@@ -987,7 +987,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>40</v>
       </c>
@@ -1001,7 +1001,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>42</v>
       </c>
@@ -1015,7 +1015,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>44</v>
       </c>
@@ -1047,7 +1047,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>10</v>
       </c>
@@ -1079,7 +1079,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>14</v>
       </c>
@@ -1111,7 +1111,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>16</v>
       </c>
@@ -1143,7 +1143,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>47</v>
       </c>
@@ -1175,7 +1175,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>24</v>
       </c>
@@ -1204,7 +1204,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>29</v>
       </c>
@@ -1236,7 +1236,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>29</v>
       </c>
@@ -1268,7 +1268,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>32</v>
       </c>
@@ -1297,7 +1297,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>32</v>
       </c>
@@ -1314,7 +1314,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>40</v>
       </c>
@@ -1328,7 +1328,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>49</v>
       </c>
@@ -1342,7 +1342,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>42</v>
       </c>
@@ -1356,7 +1356,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>51</v>
       </c>

--- a/html/Kiropraktorsystemer_excel.XLSX
+++ b/html/Kiropraktorsystemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8E83F2A-6252-43FE-AF40-38BB1B942768}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFB22091-FF00-43E3-8F65-7CF648EF20E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 02-07-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 03-07-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Kiropraktorsystemer">'Opdateret d. 02-07-2026'!$A$1:$J$32</definedName>
+    <definedName name="Kiropraktorsystemer">'Opdateret d. 03-07-2026'!$A$1:$J$32</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -524,9 +524,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J32"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -558,7 +558,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -590,7 +590,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>14</v>
       </c>
@@ -622,7 +622,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>16</v>
       </c>
@@ -654,7 +654,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>19</v>
       </c>
@@ -680,7 +680,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>21</v>
       </c>
@@ -712,7 +712,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>24</v>
       </c>
@@ -741,7 +741,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>26</v>
       </c>
@@ -764,7 +764,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>26</v>
       </c>
@@ -793,7 +793,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>29</v>
       </c>
@@ -822,7 +822,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>29</v>
       </c>
@@ -851,7 +851,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>32</v>
       </c>
@@ -880,7 +880,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>32</v>
       </c>
@@ -912,7 +912,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>35</v>
       </c>
@@ -941,7 +941,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>37</v>
       </c>
@@ -964,7 +964,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>37</v>
       </c>
@@ -987,7 +987,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>40</v>
       </c>
@@ -1001,7 +1001,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>42</v>
       </c>
@@ -1015,7 +1015,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>44</v>
       </c>
@@ -1047,7 +1047,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>10</v>
       </c>
@@ -1079,7 +1079,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>14</v>
       </c>
@@ -1111,7 +1111,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>16</v>
       </c>
@@ -1143,7 +1143,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>47</v>
       </c>
@@ -1175,7 +1175,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>24</v>
       </c>
@@ -1204,7 +1204,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>29</v>
       </c>
@@ -1236,7 +1236,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>29</v>
       </c>
@@ -1268,7 +1268,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>32</v>
       </c>
@@ -1297,7 +1297,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>32</v>
       </c>
@@ -1314,7 +1314,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>40</v>
       </c>
@@ -1328,7 +1328,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>49</v>
       </c>
@@ -1342,7 +1342,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>42</v>
       </c>
@@ -1356,7 +1356,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>51</v>
       </c>

--- a/html/Kiropraktorsystemer_excel.XLSX
+++ b/html/Kiropraktorsystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFB22091-FF00-43E3-8F65-7CF648EF20E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4109D0A8-1343-4CA2-BC2A-7B41D12815B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 03-07-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 09-07-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Kiropraktorsystemer">'Opdateret d. 03-07-2026'!$A$1:$J$32</definedName>
+    <definedName name="Kiropraktorsystemer">'Opdateret d. 09-07-2026'!$A$1:$J$32</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Kiropraktorsystemer_excel.XLSX
+++ b/html/Kiropraktorsystemer_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4109D0A8-1343-4CA2-BC2A-7B41D12815B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FC6CFC6-8350-4B68-AFD8-C9992F5EBF2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 09-07-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 19-08-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Kiropraktorsystemer">'Opdateret d. 09-07-2026'!$A$1:$J$32</definedName>
+    <definedName name="Kiropraktorsystemer">'Opdateret d. 19-08-2026'!$A$1:$J$32</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Kiropraktorsystemer_excel.XLSX
+++ b/html/Kiropraktorsystemer_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FC6CFC6-8350-4B68-AFD8-C9992F5EBF2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B2CE3E5-337A-469F-A3D9-BD1F39279118}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4560" yWindow="945" windowWidth="21600" windowHeight="12450" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 19-08-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 21-08-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Kiropraktorsystemer">'Opdateret d. 19-08-2026'!$A$1:$J$32</definedName>
+    <definedName name="Kiropraktorsystemer">'Opdateret d. 21-08-2026'!$A$1:$J$32</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -524,9 +524,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J32"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -558,7 +558,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -590,7 +590,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>14</v>
       </c>
@@ -622,7 +622,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>16</v>
       </c>
@@ -654,7 +654,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>19</v>
       </c>
@@ -680,7 +680,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>21</v>
       </c>
@@ -712,7 +712,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>24</v>
       </c>
@@ -741,7 +741,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>26</v>
       </c>
@@ -764,7 +764,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>26</v>
       </c>
@@ -793,7 +793,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>29</v>
       </c>
@@ -822,7 +822,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>29</v>
       </c>
@@ -851,7 +851,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>32</v>
       </c>
@@ -880,7 +880,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>32</v>
       </c>
@@ -912,7 +912,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>35</v>
       </c>
@@ -941,7 +941,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>37</v>
       </c>
@@ -964,7 +964,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>37</v>
       </c>
@@ -987,7 +987,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>40</v>
       </c>
@@ -1001,7 +1001,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>42</v>
       </c>
@@ -1015,7 +1015,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>44</v>
       </c>
@@ -1047,7 +1047,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>10</v>
       </c>
@@ -1079,7 +1079,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>14</v>
       </c>
@@ -1111,7 +1111,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>16</v>
       </c>
@@ -1143,7 +1143,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>47</v>
       </c>
@@ -1175,7 +1175,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>24</v>
       </c>
@@ -1204,7 +1204,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>29</v>
       </c>
@@ -1236,7 +1236,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>29</v>
       </c>
@@ -1268,7 +1268,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>32</v>
       </c>
@@ -1297,7 +1297,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>32</v>
       </c>
@@ -1314,7 +1314,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>40</v>
       </c>
@@ -1328,7 +1328,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>49</v>
       </c>
@@ -1342,7 +1342,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>42</v>
       </c>
@@ -1356,7 +1356,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>51</v>
       </c>

--- a/html/Kiropraktorsystemer_excel.XLSX
+++ b/html/Kiropraktorsystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B2CE3E5-337A-469F-A3D9-BD1F39279118}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73E4FB01-BD4F-4249-955D-582577D017CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4560" yWindow="945" windowWidth="21600" windowHeight="12450" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 21-08-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 27-08-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Kiropraktorsystemer">'Opdateret d. 21-08-2026'!$A$1:$J$32</definedName>
+    <definedName name="Kiropraktorsystemer">'Opdateret d. 27-08-2026'!$A$1:$J$32</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -524,9 +524,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J32"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -558,7 +558,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -590,7 +590,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>14</v>
       </c>
@@ -622,7 +622,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>16</v>
       </c>
@@ -654,7 +654,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>19</v>
       </c>
@@ -680,7 +680,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>21</v>
       </c>
@@ -712,7 +712,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>24</v>
       </c>
@@ -741,7 +741,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>26</v>
       </c>
@@ -764,7 +764,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>26</v>
       </c>
@@ -793,7 +793,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>29</v>
       </c>
@@ -822,7 +822,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>29</v>
       </c>
@@ -851,7 +851,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>32</v>
       </c>
@@ -880,7 +880,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>32</v>
       </c>
@@ -912,7 +912,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>35</v>
       </c>
@@ -941,7 +941,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>37</v>
       </c>
@@ -964,7 +964,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>37</v>
       </c>
@@ -987,7 +987,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>40</v>
       </c>
@@ -1001,7 +1001,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>42</v>
       </c>
@@ -1015,7 +1015,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>44</v>
       </c>
@@ -1047,7 +1047,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>10</v>
       </c>
@@ -1079,7 +1079,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>14</v>
       </c>
@@ -1111,7 +1111,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>16</v>
       </c>
@@ -1143,7 +1143,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>47</v>
       </c>
@@ -1175,7 +1175,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>24</v>
       </c>
@@ -1204,7 +1204,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>29</v>
       </c>
@@ -1236,7 +1236,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>29</v>
       </c>
@@ -1268,7 +1268,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>32</v>
       </c>
@@ -1297,7 +1297,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>32</v>
       </c>
@@ -1314,7 +1314,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>40</v>
       </c>
@@ -1328,7 +1328,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>49</v>
       </c>
@@ -1342,7 +1342,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>42</v>
       </c>
@@ -1356,7 +1356,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>51</v>
       </c>

--- a/html/Kiropraktorsystemer_excel.XLSX
+++ b/html/Kiropraktorsystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73E4FB01-BD4F-4249-955D-582577D017CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7706D47D-8B2D-4A43-8261-BE6977299C7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 27-08-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 02-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Kiropraktorsystemer">'Opdateret d. 27-08-2026'!$A$1:$J$32</definedName>
+    <definedName name="Kiropraktorsystemer">'Opdateret d. 02-09-2026'!$A$1:$J$32</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Kiropraktorsystemer_excel.XLSX
+++ b/html/Kiropraktorsystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7706D47D-8B2D-4A43-8261-BE6977299C7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8593C62-BCD7-4ADA-8668-0611661AD947}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14625" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 02-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 06-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Kiropraktorsystemer">'Opdateret d. 02-09-2026'!$A$1:$J$32</definedName>
+    <definedName name="Kiropraktorsystemer">'Opdateret d. 06-09-2026'!$A$1:$J$32</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Kiropraktorsystemer_excel.XLSX
+++ b/html/Kiropraktorsystemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8593C62-BCD7-4ADA-8668-0611661AD947}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C13AE02-A9EB-4C99-B009-88310086F6A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14625" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Kiropraktorsystemer_excel.XLSX
+++ b/html/Kiropraktorsystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C13AE02-A9EB-4C99-B009-88310086F6A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17399A8E-EC25-42BE-AC0C-EB5281074A7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14625" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 06-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 07-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Kiropraktorsystemer">'Opdateret d. 06-09-2026'!$A$1:$J$32</definedName>
+    <definedName name="Kiropraktorsystemer">'Opdateret d. 07-09-2026'!$A$1:$J$32</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Kiropraktorsystemer_excel.XLSX
+++ b/html/Kiropraktorsystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17399A8E-EC25-42BE-AC0C-EB5281074A7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58943436-3E59-4A84-B581-F285C392CA7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 07-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 09-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Kiropraktorsystemer">'Opdateret d. 07-09-2026'!$A$1:$J$32</definedName>
+    <definedName name="Kiropraktorsystemer">'Opdateret d. 09-09-2026'!$A$1:$J$32</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Kiropraktorsystemer_excel.XLSX
+++ b/html/Kiropraktorsystemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58943436-3E59-4A84-B581-F285C392CA7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7560A295-0988-4AB2-8556-275F1A67C204}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
